--- a/01-Customer-Onboarding-Workflow/02-Data-Protection-Impact-Assessment/03-Third-Party-Risk-Management/Third Party Risk Management Mock Up by Abdulmuizz.xlsx
+++ b/01-Customer-Onboarding-Workflow/02-Data-Protection-Impact-Assessment/03-Third-Party-Risk-Management/Third Party Risk Management Mock Up by Abdulmuizz.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muiz\Documents\PERSONAL\Compliance\Portfolio and Mock Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6612F9-1F09-4550-B156-F6AB90BA3D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2BCA84-F0F0-4200-A42D-639C81C2AC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{8482CBD0-A850-44F8-B97C-FAE7AD7A0EF4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{8482CBD0-A850-44F8-B97C-FAE7AD7A0EF4}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Vendor Register" sheetId="2" r:id="rId2"/>
     <sheet name="Vendor Due Diligence and Risk" sheetId="5" r:id="rId3"/>
-    <sheet name="Executive Dashboardd" sheetId="7" r:id="rId4"/>
+    <sheet name="Executive Dashboard" sheetId="7" r:id="rId4"/>
     <sheet name="Look up Table" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -675,9 +675,6 @@
     <t>Overall Due Diligence Score</t>
   </si>
   <si>
-    <t>AML/CFT COMPLIANCE DASHBOARD</t>
-  </si>
-  <si>
     <t>Risk Rating</t>
   </si>
   <si>
@@ -718,6 +715,9 @@
   </si>
   <si>
     <t>02_Vendor_Due_Diligence and Risk Assessment</t>
+  </si>
+  <si>
+    <t>AML/CFT TPRM DASHBOARD</t>
   </si>
 </sst>
 </file>
@@ -1175,7 +1175,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Executive Dashboardd'!$B$7</c:f>
+              <c:f>'Executive Dashboard'!$B$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1266,7 +1266,7 @@
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>'Executive Dashboardd'!$A$8:$A$11</c:f>
+              <c:f>'Executive Dashboard'!$A$8:$A$11</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -1286,7 +1286,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Executive Dashboardd'!$B$8:$B$11</c:f>
+              <c:f>'Executive Dashboard'!$B$8:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1486,7 +1486,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Executive Dashboardd'!$B$20</c:f>
+              <c:f>'Executive Dashboard'!$B$20</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1507,7 +1507,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Executive Dashboardd'!$A$21:$A$24</c:f>
+              <c:f>'Executive Dashboard'!$A$21:$A$24</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -1527,7 +1527,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Executive Dashboardd'!$B$21:$B$24</c:f>
+              <c:f>'Executive Dashboard'!$B$21:$B$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s">
         <v>21</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -3728,10 +3728,10 @@
         <v>61</v>
       </c>
       <c r="S1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="T1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="U1" t="s">
         <v>62</v>
@@ -3791,7 +3791,7 @@
         <v>142</v>
       </c>
       <c r="R2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S2">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -3873,7 +3873,7 @@
         <v>142</v>
       </c>
       <c r="R3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S3">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -3955,7 +3955,7 @@
         <v>142</v>
       </c>
       <c r="R4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S4">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -4037,7 +4037,7 @@
         <v>142</v>
       </c>
       <c r="R5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S5">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -4119,7 +4119,7 @@
         <v>142</v>
       </c>
       <c r="R6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S6">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -4201,7 +4201,7 @@
         <v>142</v>
       </c>
       <c r="R7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S7">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -4283,7 +4283,7 @@
         <v>142</v>
       </c>
       <c r="R8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S8">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -4365,7 +4365,7 @@
         <v>142</v>
       </c>
       <c r="R9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S9">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -4447,7 +4447,7 @@
         <v>142</v>
       </c>
       <c r="R10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S10">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -4529,7 +4529,7 @@
         <v>142</v>
       </c>
       <c r="R11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S11">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -4611,7 +4611,7 @@
         <v>142</v>
       </c>
       <c r="R12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S12">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -4693,7 +4693,7 @@
         <v>142</v>
       </c>
       <c r="R13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S13">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -4775,7 +4775,7 @@
         <v>142</v>
       </c>
       <c r="R14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S14">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -4857,7 +4857,7 @@
         <v>142</v>
       </c>
       <c r="R15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S15">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -4939,7 +4939,7 @@
         <v>142</v>
       </c>
       <c r="R16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S16">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -5021,7 +5021,7 @@
         <v>142</v>
       </c>
       <c r="R17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S17">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -5103,7 +5103,7 @@
         <v>142</v>
       </c>
       <c r="R18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S18">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -5185,7 +5185,7 @@
         <v>142</v>
       </c>
       <c r="R19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S19">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -5267,7 +5267,7 @@
         <v>142</v>
       </c>
       <c r="R20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S20">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -5349,7 +5349,7 @@
         <v>142</v>
       </c>
       <c r="R21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S21">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -5431,7 +5431,7 @@
         <v>142</v>
       </c>
       <c r="R22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S22">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -5513,7 +5513,7 @@
         <v>142</v>
       </c>
       <c r="R23" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S23">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -5595,7 +5595,7 @@
         <v>142</v>
       </c>
       <c r="R24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S24">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -5677,7 +5677,7 @@
         <v>142</v>
       </c>
       <c r="R25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S25">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -5759,7 +5759,7 @@
         <v>142</v>
       </c>
       <c r="R26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S26">
         <f>(IF(tblVendorRegister[[#This Row],[Critical Vendor?]]="Yes",3,0))
@@ -8518,7 +8518,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -8530,21 +8530,21 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B3" s="13">
         <f>COUNTA(tblVendorRegister[Vendor ID])</f>
         <v>25</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D3" s="13">
         <f>COUNTIF(tblVendorRegister[Critical Vendor?],"Yes")</f>
         <v>20</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F3" s="13">
         <f>COUNTIF(tblVendorAssessment[Overall Risk Rating],"High")
@@ -8552,13 +8552,13 @@
         <v>1</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H3" s="13">
         <v>21</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J3" s="13">
         <f>ROUND(
@@ -8586,10 +8586,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>200</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -8629,10 +8629,10 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -8655,7 +8655,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B23" s="10">
         <f>COUNTIF(tblVendorAssessment[Overall Control Effectiveness],"Moderate")</f>
